--- a/artfynd/A 31953-2021 artfynd.xlsx
+++ b/artfynd/A 31953-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31953-2021 artfynd.xlsx
+++ b/artfynd/A 31953-2021 artfynd.xlsx
@@ -675,50 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95937619</v>
+        <v>96785791</v>
       </c>
       <c r="B2" t="n">
-        <v>90339</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4787</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Edefjället, Jmt</t>
+          <t>Mellan Edefjället och Sösjöån, mellan Sösjön och Torrön, ca 15 km nordos..., Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406728.6946778646</v>
+        <v>406745</v>
       </c>
       <c r="R2" t="n">
-        <v>7081495.707031051</v>
+        <v>7081291</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,18 +757,34 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>i äldre granskog med högt björkinslag</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>på ved på högstubbe av björk ca 20 cm i diameter</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linda Johannesson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linda Johannesson, Jesper Wadstein</t>
+          <t>Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,12 +794,7 @@
         <v>95937616</v>
       </c>
       <c r="B3" t="n">
-        <v>73698</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406714.4453062335</v>
+        <v>406714</v>
       </c>
       <c r="R3" t="n">
-        <v>7081447.572939422</v>
+        <v>7081448</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +859,9 @@
           <t>2021-07-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,15 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95937614</v>
+        <v>95937619</v>
       </c>
       <c r="B4" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>4787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>406703.8827447465</v>
+        <v>406729</v>
       </c>
       <c r="R4" t="n">
-        <v>7081255.855901087</v>
+        <v>7081496</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +961,9 @@
           <t>2021-07-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-07-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,37 +990,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96785793</v>
+        <v>96785784</v>
       </c>
       <c r="B5" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>406453.4192028831</v>
+        <v>406788</v>
       </c>
       <c r="R5" t="n">
-        <v>7081276.556915635</v>
+        <v>7081579</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,19 +1061,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,12 +1078,12 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>i gransumpskog 4 m bäck</t>
+          <t>i gammal granskog nära bäck, lite bördigare just här</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>på bark på stam av levande gran ca 55 cm i diameter</t>
+          <t>på gran ca 40 cm i diameter</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -1147,15 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96785789</v>
+        <v>96785790</v>
       </c>
       <c r="B6" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,21 +1117,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>406788.6470373008</v>
+        <v>406788</v>
       </c>
       <c r="R6" t="n">
-        <v>7081579.561618184</v>
+        <v>7081579</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,19 +1177,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1281,12 +1225,7 @@
         <v>96785794</v>
       </c>
       <c r="B7" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>406453.4192028831</v>
+        <v>406454</v>
       </c>
       <c r="R7" t="n">
-        <v>7081276.556915635</v>
+        <v>7081276</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1354,19 +1293,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1409,53 +1338,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96785784</v>
+        <v>95937614</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mellan Edefjället och Sösjöån, mellan Sösjön och Torrön, ca 15 km nordos..., Jmt</t>
+          <t>Edefjället, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>406788.6470373008</v>
+        <v>406704</v>
       </c>
       <c r="R8" t="n">
-        <v>7081579.561618184</v>
+        <v>7081255</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1482,22 +1403,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,49 +1417,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>i gammal granskog nära bäck, lite bördigare just här</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>på gran ca 40 cm i diameter</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Linda Johannesson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Linda Johannesson, Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96785790</v>
+        <v>96785789</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,21 +1446,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1583,10 +1473,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>406788.6470373008</v>
+        <v>406788</v>
       </c>
       <c r="R9" t="n">
-        <v>7081579.561618184</v>
+        <v>7081579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,19 +1506,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,15 +1551,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96785791</v>
+        <v>96785793</v>
       </c>
       <c r="B10" t="n">
-        <v>73686</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,21 +1562,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1714,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>406745.1611026767</v>
+        <v>406454</v>
       </c>
       <c r="R10" t="n">
-        <v>7081291.270139787</v>
+        <v>7081276</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1747,19 +1622,9 @@
           <t>2016-10-20</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2016-10-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1774,12 +1639,12 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>i äldre granskog med högt björkinslag</t>
+          <t>i gransumpskog 4 m bäck</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>på ved på högstubbe av björk ca 20 cm i diameter</t>
+          <t>på bark på stam av levande gran ca 55 cm i diameter</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
